--- a/template.xlsx
+++ b/template.xlsx
@@ -216,7 +216,22 @@
         <t>Pubmed reference / URL / or submitter details in case unpublished.</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Frequency of this clonotype in the isolated epitope-reactive population, as the submitter wrote it: `x/X`, `X%` or a bare float. Free text on purpose - it is what every release has shipped, and some studies report only the ratio.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Reads, UMIs or cells supporting this clonotype, parsed from an unambiguous `x/X` `method.frequency`. Null where the submitted value is a float or a percentage: the count is absent, not zero.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>The sample total `method.frequency.count` is out of, from the same `x/X`.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>Kept for debugging; dropped by the legacy build.</t>
       </text>
@@ -534,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG105"/>
+  <dimension ref="A1:AI105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -555,21 +570,23 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="23" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="19" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="17" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -665,75 +682,85 @@
       </c>
       <c r="S1" s="3" t="inlineStr">
         <is>
+          <t>method.frequency.count</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>method.frequency.total</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
           <t>method.singlecell</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>method.sequencing</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>method.verification</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>meta.study.id</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>meta.cell.subset</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>meta.subset.frequency</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>meta.subject.cohort</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>meta.subject.id</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>meta.replica.id</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>meta.clone.id</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>meta.epitope.id</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>meta.tissue</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>meta.donor.MHC</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>meta.donor.MHC.method</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>meta.structure.id</t>
         </is>
@@ -824,13 +851,13 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr"/>
-      <c r="W2" s="5" t="inlineStr"/>
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr"/>
       <c r="Z2" s="5" t="inlineStr"/>
@@ -840,7 +867,9 @@
       <c r="AD2" s="5" t="inlineStr"/>
       <c r="AE2" s="5" t="inlineStr"/>
       <c r="AF2" s="5" t="inlineStr"/>
-      <c r="AG2" s="5" t="inlineStr">
+      <c r="AG2" s="5" t="inlineStr"/>
+      <c r="AH2" s="5" t="inlineStr"/>
+      <c r="AI2" s="5" t="inlineStr">
         <is>
           <t>1AO7</t>
         </is>
@@ -935,51 +964,61 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>sanger</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>antigen-loaded-targets,direct</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr"/>
-      <c r="W3" s="5" t="inlineStr">
-        <is>
-          <t>CD4+</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr"/>
       <c r="Y3" s="5" t="inlineStr">
         <is>
+          <t>CD4+</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
           <t>Sjogren's Disease</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr"/>
-      <c r="AA3" s="5" t="inlineStr"/>
-      <c r="AB3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr"/>
+      <c r="AC3" s="5" t="inlineStr"/>
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>P106</t>
         </is>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AF3" s="5" t="inlineStr">
         <is>
           <t>Salivary Gland</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr"/>
-      <c r="AF3" s="5" t="inlineStr"/>
       <c r="AG3" s="5" t="inlineStr"/>
+      <c r="AH3" s="5" t="inlineStr"/>
+      <c r="AI3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1061,40 +1100,42 @@
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>sanger</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr"/>
-      <c r="W4" s="5" t="inlineStr">
-        <is>
-          <t>CD8+</t>
-        </is>
-      </c>
+      <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr">
         <is>
+          <t>CD8+</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr"/>
-      <c r="AB4" s="5" t="inlineStr"/>
       <c r="AC4" s="5" t="inlineStr"/>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr"/>
+      <c r="AE4" s="5" t="inlineStr"/>
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>Polyclonal T-cell line</t>
         </is>
       </c>
-      <c r="AE4" s="5" t="inlineStr"/>
-      <c r="AF4" s="5" t="inlineStr"/>
       <c r="AG4" s="5" t="inlineStr"/>
+      <c r="AH4" s="5" t="inlineStr"/>
+      <c r="AI4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1171,33 +1212,35 @@
           <t>1/86</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>rna-seq</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr"/>
       <c r="W5" s="5" t="inlineStr"/>
       <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr">
         <is>
           <t>C57BL/6 immunized with LCMV</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="inlineStr"/>
-      <c r="AA5" s="5" t="inlineStr"/>
       <c r="AB5" s="5" t="inlineStr"/>
       <c r="AC5" s="5" t="inlineStr"/>
       <c r="AD5" s="5" t="inlineStr"/>
       <c r="AE5" s="5" t="inlineStr"/>
       <c r="AF5" s="5" t="inlineStr"/>
       <c r="AG5" s="5" t="inlineStr"/>
+      <c r="AH5" s="5" t="inlineStr"/>
+      <c r="AI5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1233,6 +1276,8 @@
       <c r="AE6" s="5" t="n"/>
       <c r="AF6" s="5" t="n"/>
       <c r="AG6" s="5" t="n"/>
+      <c r="AH6" s="5" t="n"/>
+      <c r="AI6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1268,6 +1313,8 @@
       <c r="AE7" s="5" t="n"/>
       <c r="AF7" s="5" t="n"/>
       <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1303,6 +1350,8 @@
       <c r="AE8" s="5" t="n"/>
       <c r="AF8" s="5" t="n"/>
       <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1338,6 +1387,8 @@
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
       <c r="AG9" s="5" t="n"/>
+      <c r="AH9" s="5" t="n"/>
+      <c r="AI9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1373,6 +1424,8 @@
       <c r="AE10" s="5" t="n"/>
       <c r="AF10" s="5" t="n"/>
       <c r="AG10" s="5" t="n"/>
+      <c r="AH10" s="5" t="n"/>
+      <c r="AI10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1408,6 +1461,8 @@
       <c r="AE11" s="5" t="n"/>
       <c r="AF11" s="5" t="n"/>
       <c r="AG11" s="5" t="n"/>
+      <c r="AH11" s="5" t="n"/>
+      <c r="AI11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1443,6 +1498,8 @@
       <c r="AE12" s="5" t="n"/>
       <c r="AF12" s="5" t="n"/>
       <c r="AG12" s="5" t="n"/>
+      <c r="AH12" s="5" t="n"/>
+      <c r="AI12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1478,6 +1535,8 @@
       <c r="AE13" s="5" t="n"/>
       <c r="AF13" s="5" t="n"/>
       <c r="AG13" s="5" t="n"/>
+      <c r="AH13" s="5" t="n"/>
+      <c r="AI13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1513,6 +1572,8 @@
       <c r="AE14" s="5" t="n"/>
       <c r="AF14" s="5" t="n"/>
       <c r="AG14" s="5" t="n"/>
+      <c r="AH14" s="5" t="n"/>
+      <c r="AI14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1548,6 +1609,8 @@
       <c r="AE15" s="5" t="n"/>
       <c r="AF15" s="5" t="n"/>
       <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1583,6 +1646,8 @@
       <c r="AE16" s="5" t="n"/>
       <c r="AF16" s="5" t="n"/>
       <c r="AG16" s="5" t="n"/>
+      <c r="AH16" s="5" t="n"/>
+      <c r="AI16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1618,6 +1683,8 @@
       <c r="AE17" s="5" t="n"/>
       <c r="AF17" s="5" t="n"/>
       <c r="AG17" s="5" t="n"/>
+      <c r="AH17" s="5" t="n"/>
+      <c r="AI17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1653,6 +1720,8 @@
       <c r="AE18" s="5" t="n"/>
       <c r="AF18" s="5" t="n"/>
       <c r="AG18" s="5" t="n"/>
+      <c r="AH18" s="5" t="n"/>
+      <c r="AI18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1688,6 +1757,8 @@
       <c r="AE19" s="5" t="n"/>
       <c r="AF19" s="5" t="n"/>
       <c r="AG19" s="5" t="n"/>
+      <c r="AH19" s="5" t="n"/>
+      <c r="AI19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1723,6 +1794,8 @@
       <c r="AE20" s="5" t="n"/>
       <c r="AF20" s="5" t="n"/>
       <c r="AG20" s="5" t="n"/>
+      <c r="AH20" s="5" t="n"/>
+      <c r="AI20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1758,6 +1831,8 @@
       <c r="AE21" s="5" t="n"/>
       <c r="AF21" s="5" t="n"/>
       <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1793,6 +1868,8 @@
       <c r="AE22" s="5" t="n"/>
       <c r="AF22" s="5" t="n"/>
       <c r="AG22" s="5" t="n"/>
+      <c r="AH22" s="5" t="n"/>
+      <c r="AI22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1828,6 +1905,8 @@
       <c r="AE23" s="5" t="n"/>
       <c r="AF23" s="5" t="n"/>
       <c r="AG23" s="5" t="n"/>
+      <c r="AH23" s="5" t="n"/>
+      <c r="AI23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1863,6 +1942,8 @@
       <c r="AE24" s="5" t="n"/>
       <c r="AF24" s="5" t="n"/>
       <c r="AG24" s="5" t="n"/>
+      <c r="AH24" s="5" t="n"/>
+      <c r="AI24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1898,6 +1979,8 @@
       <c r="AE25" s="5" t="n"/>
       <c r="AF25" s="5" t="n"/>
       <c r="AG25" s="5" t="n"/>
+      <c r="AH25" s="5" t="n"/>
+      <c r="AI25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1933,6 +2016,8 @@
       <c r="AE26" s="5" t="n"/>
       <c r="AF26" s="5" t="n"/>
       <c r="AG26" s="5" t="n"/>
+      <c r="AH26" s="5" t="n"/>
+      <c r="AI26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1968,6 +2053,8 @@
       <c r="AE27" s="5" t="n"/>
       <c r="AF27" s="5" t="n"/>
       <c r="AG27" s="5" t="n"/>
+      <c r="AH27" s="5" t="n"/>
+      <c r="AI27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -2003,6 +2090,8 @@
       <c r="AE28" s="5" t="n"/>
       <c r="AF28" s="5" t="n"/>
       <c r="AG28" s="5" t="n"/>
+      <c r="AH28" s="5" t="n"/>
+      <c r="AI28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -2038,6 +2127,8 @@
       <c r="AE29" s="5" t="n"/>
       <c r="AF29" s="5" t="n"/>
       <c r="AG29" s="5" t="n"/>
+      <c r="AH29" s="5" t="n"/>
+      <c r="AI29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -2073,6 +2164,8 @@
       <c r="AE30" s="5" t="n"/>
       <c r="AF30" s="5" t="n"/>
       <c r="AG30" s="5" t="n"/>
+      <c r="AH30" s="5" t="n"/>
+      <c r="AI30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -2108,6 +2201,8 @@
       <c r="AE31" s="5" t="n"/>
       <c r="AF31" s="5" t="n"/>
       <c r="AG31" s="5" t="n"/>
+      <c r="AH31" s="5" t="n"/>
+      <c r="AI31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -2143,6 +2238,8 @@
       <c r="AE32" s="5" t="n"/>
       <c r="AF32" s="5" t="n"/>
       <c r="AG32" s="5" t="n"/>
+      <c r="AH32" s="5" t="n"/>
+      <c r="AI32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -2178,6 +2275,8 @@
       <c r="AE33" s="5" t="n"/>
       <c r="AF33" s="5" t="n"/>
       <c r="AG33" s="5" t="n"/>
+      <c r="AH33" s="5" t="n"/>
+      <c r="AI33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -2213,6 +2312,8 @@
       <c r="AE34" s="5" t="n"/>
       <c r="AF34" s="5" t="n"/>
       <c r="AG34" s="5" t="n"/>
+      <c r="AH34" s="5" t="n"/>
+      <c r="AI34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -2248,6 +2349,8 @@
       <c r="AE35" s="5" t="n"/>
       <c r="AF35" s="5" t="n"/>
       <c r="AG35" s="5" t="n"/>
+      <c r="AH35" s="5" t="n"/>
+      <c r="AI35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -2283,6 +2386,8 @@
       <c r="AE36" s="5" t="n"/>
       <c r="AF36" s="5" t="n"/>
       <c r="AG36" s="5" t="n"/>
+      <c r="AH36" s="5" t="n"/>
+      <c r="AI36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -2318,6 +2423,8 @@
       <c r="AE37" s="5" t="n"/>
       <c r="AF37" s="5" t="n"/>
       <c r="AG37" s="5" t="n"/>
+      <c r="AH37" s="5" t="n"/>
+      <c r="AI37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -2353,6 +2460,8 @@
       <c r="AE38" s="5" t="n"/>
       <c r="AF38" s="5" t="n"/>
       <c r="AG38" s="5" t="n"/>
+      <c r="AH38" s="5" t="n"/>
+      <c r="AI38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -2388,6 +2497,8 @@
       <c r="AE39" s="5" t="n"/>
       <c r="AF39" s="5" t="n"/>
       <c r="AG39" s="5" t="n"/>
+      <c r="AH39" s="5" t="n"/>
+      <c r="AI39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -2423,6 +2534,8 @@
       <c r="AE40" s="5" t="n"/>
       <c r="AF40" s="5" t="n"/>
       <c r="AG40" s="5" t="n"/>
+      <c r="AH40" s="5" t="n"/>
+      <c r="AI40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -2458,6 +2571,8 @@
       <c r="AE41" s="5" t="n"/>
       <c r="AF41" s="5" t="n"/>
       <c r="AG41" s="5" t="n"/>
+      <c r="AH41" s="5" t="n"/>
+      <c r="AI41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -2493,6 +2608,8 @@
       <c r="AE42" s="5" t="n"/>
       <c r="AF42" s="5" t="n"/>
       <c r="AG42" s="5" t="n"/>
+      <c r="AH42" s="5" t="n"/>
+      <c r="AI42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -2528,6 +2645,8 @@
       <c r="AE43" s="5" t="n"/>
       <c r="AF43" s="5" t="n"/>
       <c r="AG43" s="5" t="n"/>
+      <c r="AH43" s="5" t="n"/>
+      <c r="AI43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -2563,6 +2682,8 @@
       <c r="AE44" s="5" t="n"/>
       <c r="AF44" s="5" t="n"/>
       <c r="AG44" s="5" t="n"/>
+      <c r="AH44" s="5" t="n"/>
+      <c r="AI44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -2598,6 +2719,8 @@
       <c r="AE45" s="5" t="n"/>
       <c r="AF45" s="5" t="n"/>
       <c r="AG45" s="5" t="n"/>
+      <c r="AH45" s="5" t="n"/>
+      <c r="AI45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -2633,6 +2756,8 @@
       <c r="AE46" s="5" t="n"/>
       <c r="AF46" s="5" t="n"/>
       <c r="AG46" s="5" t="n"/>
+      <c r="AH46" s="5" t="n"/>
+      <c r="AI46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -2668,6 +2793,8 @@
       <c r="AE47" s="5" t="n"/>
       <c r="AF47" s="5" t="n"/>
       <c r="AG47" s="5" t="n"/>
+      <c r="AH47" s="5" t="n"/>
+      <c r="AI47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2703,6 +2830,8 @@
       <c r="AE48" s="5" t="n"/>
       <c r="AF48" s="5" t="n"/>
       <c r="AG48" s="5" t="n"/>
+      <c r="AH48" s="5" t="n"/>
+      <c r="AI48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2738,6 +2867,8 @@
       <c r="AE49" s="5" t="n"/>
       <c r="AF49" s="5" t="n"/>
       <c r="AG49" s="5" t="n"/>
+      <c r="AH49" s="5" t="n"/>
+      <c r="AI49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2773,6 +2904,8 @@
       <c r="AE50" s="5" t="n"/>
       <c r="AF50" s="5" t="n"/>
       <c r="AG50" s="5" t="n"/>
+      <c r="AH50" s="5" t="n"/>
+      <c r="AI50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2808,6 +2941,8 @@
       <c r="AE51" s="5" t="n"/>
       <c r="AF51" s="5" t="n"/>
       <c r="AG51" s="5" t="n"/>
+      <c r="AH51" s="5" t="n"/>
+      <c r="AI51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -2843,6 +2978,8 @@
       <c r="AE52" s="5" t="n"/>
       <c r="AF52" s="5" t="n"/>
       <c r="AG52" s="5" t="n"/>
+      <c r="AH52" s="5" t="n"/>
+      <c r="AI52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -2878,6 +3015,8 @@
       <c r="AE53" s="5" t="n"/>
       <c r="AF53" s="5" t="n"/>
       <c r="AG53" s="5" t="n"/>
+      <c r="AH53" s="5" t="n"/>
+      <c r="AI53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -2913,6 +3052,8 @@
       <c r="AE54" s="5" t="n"/>
       <c r="AF54" s="5" t="n"/>
       <c r="AG54" s="5" t="n"/>
+      <c r="AH54" s="5" t="n"/>
+      <c r="AI54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -2948,6 +3089,8 @@
       <c r="AE55" s="5" t="n"/>
       <c r="AF55" s="5" t="n"/>
       <c r="AG55" s="5" t="n"/>
+      <c r="AH55" s="5" t="n"/>
+      <c r="AI55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -2983,6 +3126,8 @@
       <c r="AE56" s="5" t="n"/>
       <c r="AF56" s="5" t="n"/>
       <c r="AG56" s="5" t="n"/>
+      <c r="AH56" s="5" t="n"/>
+      <c r="AI56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -3018,6 +3163,8 @@
       <c r="AE57" s="5" t="n"/>
       <c r="AF57" s="5" t="n"/>
       <c r="AG57" s="5" t="n"/>
+      <c r="AH57" s="5" t="n"/>
+      <c r="AI57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -3053,6 +3200,8 @@
       <c r="AE58" s="5" t="n"/>
       <c r="AF58" s="5" t="n"/>
       <c r="AG58" s="5" t="n"/>
+      <c r="AH58" s="5" t="n"/>
+      <c r="AI58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -3088,6 +3237,8 @@
       <c r="AE59" s="5" t="n"/>
       <c r="AF59" s="5" t="n"/>
       <c r="AG59" s="5" t="n"/>
+      <c r="AH59" s="5" t="n"/>
+      <c r="AI59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -3123,6 +3274,8 @@
       <c r="AE60" s="5" t="n"/>
       <c r="AF60" s="5" t="n"/>
       <c r="AG60" s="5" t="n"/>
+      <c r="AH60" s="5" t="n"/>
+      <c r="AI60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -3158,6 +3311,8 @@
       <c r="AE61" s="5" t="n"/>
       <c r="AF61" s="5" t="n"/>
       <c r="AG61" s="5" t="n"/>
+      <c r="AH61" s="5" t="n"/>
+      <c r="AI61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -3193,6 +3348,8 @@
       <c r="AE62" s="5" t="n"/>
       <c r="AF62" s="5" t="n"/>
       <c r="AG62" s="5" t="n"/>
+      <c r="AH62" s="5" t="n"/>
+      <c r="AI62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -3228,6 +3385,8 @@
       <c r="AE63" s="5" t="n"/>
       <c r="AF63" s="5" t="n"/>
       <c r="AG63" s="5" t="n"/>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -3263,6 +3422,8 @@
       <c r="AE64" s="5" t="n"/>
       <c r="AF64" s="5" t="n"/>
       <c r="AG64" s="5" t="n"/>
+      <c r="AH64" s="5" t="n"/>
+      <c r="AI64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -3298,6 +3459,8 @@
       <c r="AE65" s="5" t="n"/>
       <c r="AF65" s="5" t="n"/>
       <c r="AG65" s="5" t="n"/>
+      <c r="AH65" s="5" t="n"/>
+      <c r="AI65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -3333,6 +3496,8 @@
       <c r="AE66" s="5" t="n"/>
       <c r="AF66" s="5" t="n"/>
       <c r="AG66" s="5" t="n"/>
+      <c r="AH66" s="5" t="n"/>
+      <c r="AI66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -3368,6 +3533,8 @@
       <c r="AE67" s="5" t="n"/>
       <c r="AF67" s="5" t="n"/>
       <c r="AG67" s="5" t="n"/>
+      <c r="AH67" s="5" t="n"/>
+      <c r="AI67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -3403,6 +3570,8 @@
       <c r="AE68" s="5" t="n"/>
       <c r="AF68" s="5" t="n"/>
       <c r="AG68" s="5" t="n"/>
+      <c r="AH68" s="5" t="n"/>
+      <c r="AI68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -3438,6 +3607,8 @@
       <c r="AE69" s="5" t="n"/>
       <c r="AF69" s="5" t="n"/>
       <c r="AG69" s="5" t="n"/>
+      <c r="AH69" s="5" t="n"/>
+      <c r="AI69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -3473,6 +3644,8 @@
       <c r="AE70" s="5" t="n"/>
       <c r="AF70" s="5" t="n"/>
       <c r="AG70" s="5" t="n"/>
+      <c r="AH70" s="5" t="n"/>
+      <c r="AI70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -3508,6 +3681,8 @@
       <c r="AE71" s="5" t="n"/>
       <c r="AF71" s="5" t="n"/>
       <c r="AG71" s="5" t="n"/>
+      <c r="AH71" s="5" t="n"/>
+      <c r="AI71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -3543,6 +3718,8 @@
       <c r="AE72" s="5" t="n"/>
       <c r="AF72" s="5" t="n"/>
       <c r="AG72" s="5" t="n"/>
+      <c r="AH72" s="5" t="n"/>
+      <c r="AI72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -3578,6 +3755,8 @@
       <c r="AE73" s="5" t="n"/>
       <c r="AF73" s="5" t="n"/>
       <c r="AG73" s="5" t="n"/>
+      <c r="AH73" s="5" t="n"/>
+      <c r="AI73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -3613,6 +3792,8 @@
       <c r="AE74" s="5" t="n"/>
       <c r="AF74" s="5" t="n"/>
       <c r="AG74" s="5" t="n"/>
+      <c r="AH74" s="5" t="n"/>
+      <c r="AI74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -3648,6 +3829,8 @@
       <c r="AE75" s="5" t="n"/>
       <c r="AF75" s="5" t="n"/>
       <c r="AG75" s="5" t="n"/>
+      <c r="AH75" s="5" t="n"/>
+      <c r="AI75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -3683,6 +3866,8 @@
       <c r="AE76" s="5" t="n"/>
       <c r="AF76" s="5" t="n"/>
       <c r="AG76" s="5" t="n"/>
+      <c r="AH76" s="5" t="n"/>
+      <c r="AI76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -3718,6 +3903,8 @@
       <c r="AE77" s="5" t="n"/>
       <c r="AF77" s="5" t="n"/>
       <c r="AG77" s="5" t="n"/>
+      <c r="AH77" s="5" t="n"/>
+      <c r="AI77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -3753,6 +3940,8 @@
       <c r="AE78" s="5" t="n"/>
       <c r="AF78" s="5" t="n"/>
       <c r="AG78" s="5" t="n"/>
+      <c r="AH78" s="5" t="n"/>
+      <c r="AI78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -3788,6 +3977,8 @@
       <c r="AE79" s="5" t="n"/>
       <c r="AF79" s="5" t="n"/>
       <c r="AG79" s="5" t="n"/>
+      <c r="AH79" s="5" t="n"/>
+      <c r="AI79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -3823,6 +4014,8 @@
       <c r="AE80" s="5" t="n"/>
       <c r="AF80" s="5" t="n"/>
       <c r="AG80" s="5" t="n"/>
+      <c r="AH80" s="5" t="n"/>
+      <c r="AI80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -3858,6 +4051,8 @@
       <c r="AE81" s="5" t="n"/>
       <c r="AF81" s="5" t="n"/>
       <c r="AG81" s="5" t="n"/>
+      <c r="AH81" s="5" t="n"/>
+      <c r="AI81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -3893,6 +4088,8 @@
       <c r="AE82" s="5" t="n"/>
       <c r="AF82" s="5" t="n"/>
       <c r="AG82" s="5" t="n"/>
+      <c r="AH82" s="5" t="n"/>
+      <c r="AI82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -3928,6 +4125,8 @@
       <c r="AE83" s="5" t="n"/>
       <c r="AF83" s="5" t="n"/>
       <c r="AG83" s="5" t="n"/>
+      <c r="AH83" s="5" t="n"/>
+      <c r="AI83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -3963,6 +4162,8 @@
       <c r="AE84" s="5" t="n"/>
       <c r="AF84" s="5" t="n"/>
       <c r="AG84" s="5" t="n"/>
+      <c r="AH84" s="5" t="n"/>
+      <c r="AI84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -3998,6 +4199,8 @@
       <c r="AE85" s="5" t="n"/>
       <c r="AF85" s="5" t="n"/>
       <c r="AG85" s="5" t="n"/>
+      <c r="AH85" s="5" t="n"/>
+      <c r="AI85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -4033,6 +4236,8 @@
       <c r="AE86" s="5" t="n"/>
       <c r="AF86" s="5" t="n"/>
       <c r="AG86" s="5" t="n"/>
+      <c r="AH86" s="5" t="n"/>
+      <c r="AI86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -4068,6 +4273,8 @@
       <c r="AE87" s="5" t="n"/>
       <c r="AF87" s="5" t="n"/>
       <c r="AG87" s="5" t="n"/>
+      <c r="AH87" s="5" t="n"/>
+      <c r="AI87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -4103,6 +4310,8 @@
       <c r="AE88" s="5" t="n"/>
       <c r="AF88" s="5" t="n"/>
       <c r="AG88" s="5" t="n"/>
+      <c r="AH88" s="5" t="n"/>
+      <c r="AI88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -4138,6 +4347,8 @@
       <c r="AE89" s="5" t="n"/>
       <c r="AF89" s="5" t="n"/>
       <c r="AG89" s="5" t="n"/>
+      <c r="AH89" s="5" t="n"/>
+      <c r="AI89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -4173,6 +4384,8 @@
       <c r="AE90" s="5" t="n"/>
       <c r="AF90" s="5" t="n"/>
       <c r="AG90" s="5" t="n"/>
+      <c r="AH90" s="5" t="n"/>
+      <c r="AI90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -4208,6 +4421,8 @@
       <c r="AE91" s="5" t="n"/>
       <c r="AF91" s="5" t="n"/>
       <c r="AG91" s="5" t="n"/>
+      <c r="AH91" s="5" t="n"/>
+      <c r="AI91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -4243,6 +4458,8 @@
       <c r="AE92" s="5" t="n"/>
       <c r="AF92" s="5" t="n"/>
       <c r="AG92" s="5" t="n"/>
+      <c r="AH92" s="5" t="n"/>
+      <c r="AI92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -4278,6 +4495,8 @@
       <c r="AE93" s="5" t="n"/>
       <c r="AF93" s="5" t="n"/>
       <c r="AG93" s="5" t="n"/>
+      <c r="AH93" s="5" t="n"/>
+      <c r="AI93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -4313,6 +4532,8 @@
       <c r="AE94" s="5" t="n"/>
       <c r="AF94" s="5" t="n"/>
       <c r="AG94" s="5" t="n"/>
+      <c r="AH94" s="5" t="n"/>
+      <c r="AI94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -4348,6 +4569,8 @@
       <c r="AE95" s="5" t="n"/>
       <c r="AF95" s="5" t="n"/>
       <c r="AG95" s="5" t="n"/>
+      <c r="AH95" s="5" t="n"/>
+      <c r="AI95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -4383,6 +4606,8 @@
       <c r="AE96" s="5" t="n"/>
       <c r="AF96" s="5" t="n"/>
       <c r="AG96" s="5" t="n"/>
+      <c r="AH96" s="5" t="n"/>
+      <c r="AI96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -4418,6 +4643,8 @@
       <c r="AE97" s="5" t="n"/>
       <c r="AF97" s="5" t="n"/>
       <c r="AG97" s="5" t="n"/>
+      <c r="AH97" s="5" t="n"/>
+      <c r="AI97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -4453,6 +4680,8 @@
       <c r="AE98" s="5" t="n"/>
       <c r="AF98" s="5" t="n"/>
       <c r="AG98" s="5" t="n"/>
+      <c r="AH98" s="5" t="n"/>
+      <c r="AI98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -4488,6 +4717,8 @@
       <c r="AE99" s="5" t="n"/>
       <c r="AF99" s="5" t="n"/>
       <c r="AG99" s="5" t="n"/>
+      <c r="AH99" s="5" t="n"/>
+      <c r="AI99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -4523,6 +4754,8 @@
       <c r="AE100" s="5" t="n"/>
       <c r="AF100" s="5" t="n"/>
       <c r="AG100" s="5" t="n"/>
+      <c r="AH100" s="5" t="n"/>
+      <c r="AI100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -4558,6 +4791,8 @@
       <c r="AE101" s="5" t="n"/>
       <c r="AF101" s="5" t="n"/>
       <c r="AG101" s="5" t="n"/>
+      <c r="AH101" s="5" t="n"/>
+      <c r="AI101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -4593,6 +4828,8 @@
       <c r="AE102" s="5" t="n"/>
       <c r="AF102" s="5" t="n"/>
       <c r="AG102" s="5" t="n"/>
+      <c r="AH102" s="5" t="n"/>
+      <c r="AI102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -4628,6 +4865,8 @@
       <c r="AE103" s="5" t="n"/>
       <c r="AF103" s="5" t="n"/>
       <c r="AG103" s="5" t="n"/>
+      <c r="AH103" s="5" t="n"/>
+      <c r="AI103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -4663,6 +4902,8 @@
       <c r="AE104" s="5" t="n"/>
       <c r="AF104" s="5" t="n"/>
       <c r="AG104" s="5" t="n"/>
+      <c r="AH104" s="5" t="n"/>
+      <c r="AI104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -4698,6 +4939,8 @@
       <c r="AE105" s="5" t="n"/>
       <c r="AF105" s="5" t="n"/>
       <c r="AG105" s="5" t="n"/>
+      <c r="AH105" s="5" t="n"/>
+      <c r="AI105" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4711,7 +4954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5011,12 +5254,16 @@
           <t>method</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Frequency of this clonotype in the isolated epitope-reactive population, as the submitter wrote it: `x/X`, `X%` or a bare float. Free text on purpose - it is what every release has shipped, and some studies report only the ratio.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>method.singlecell</t>
+          <t>method.frequency.count</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5024,12 +5271,16 @@
           <t>method</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Reads, UMIs or cells supporting this clonotype, parsed from an unambiguous `x/X` `method.frequency`. Null where the submitted value is a float or a percentage: the count is absent, not zero.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>method.sequencing</t>
+          <t>method.frequency.total</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5037,12 +5288,16 @@
           <t>method</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>The sample total `method.frequency.count` is out of, from the same `x/X`.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>method.verification</t>
+          <t>method.singlecell</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5055,12 +5310,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta.study.id</t>
+          <t>method.sequencing</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr"/>
@@ -5068,12 +5323,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta.cell.subset</t>
+          <t>method.verification</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>method</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr"/>
@@ -5081,7 +5336,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meta.subset.frequency</t>
+          <t>meta.study.id</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5089,16 +5344,12 @@
           <t>meta</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Kept for debugging; dropped by the legacy build.</t>
-        </is>
-      </c>
+      <c r="C27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta.subject.cohort</t>
+          <t>meta.cell.subset</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5111,7 +5362,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta.subject.id</t>
+          <t>meta.subset.frequency</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5119,12 +5370,16 @@
           <t>meta</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Kept for debugging; dropped by the legacy build.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>meta.replica.id</t>
+          <t>meta.subject.cohort</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5137,7 +5392,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meta.clone.id</t>
+          <t>meta.subject.id</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5150,7 +5405,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meta.epitope.id</t>
+          <t>meta.replica.id</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5163,7 +5418,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meta.tissue</t>
+          <t>meta.clone.id</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5176,7 +5431,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>meta.donor.MHC</t>
+          <t>meta.epitope.id</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5189,7 +5444,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>meta.donor.MHC.method</t>
+          <t>meta.tissue</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5202,15 +5457,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>meta.donor.MHC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>meta.donor.MHC.method</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>meta.structure.id</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>meta</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
